--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,536 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113511118</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79196</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>552393</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7037722</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113508003</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>112</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7037714</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113511116</v>
+      </c>
+      <c r="B6" t="n">
+        <v>81874</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552431</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7037803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113511119</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78133</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552391</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037720</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113508002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90075</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västvattnet, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552462</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7037800</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Lindén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511118</v>
+        <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>79196</v>
+        <v>81896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552393</v>
+        <v>552431</v>
       </c>
       <c r="R4" t="n">
-        <v>7037722</v>
+        <v>7037803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113508003</v>
+        <v>113511118</v>
       </c>
       <c r="B5" t="n">
-        <v>90003</v>
+        <v>79218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552365</v>
+        <v>552393</v>
       </c>
       <c r="R5" t="n">
-        <v>7037714</v>
+        <v>7037722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511116</v>
+        <v>113508002</v>
       </c>
       <c r="B6" t="n">
-        <v>81874</v>
+        <v>90097</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552431</v>
+        <v>552462</v>
       </c>
       <c r="R6" t="n">
-        <v>7037803</v>
+        <v>7037800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511119</v>
+        <v>113508003</v>
       </c>
       <c r="B7" t="n">
-        <v>78133</v>
+        <v>90025</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552391</v>
+        <v>552365</v>
       </c>
       <c r="R7" t="n">
-        <v>7037720</v>
+        <v>7037714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113508002</v>
+        <v>113511119</v>
       </c>
       <c r="B8" t="n">
-        <v>90075</v>
+        <v>78155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552462</v>
+        <v>552391</v>
       </c>
       <c r="R8" t="n">
-        <v>7037800</v>
+        <v>7037720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>81896</v>
+        <v>81900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511118</v>
+        <v>113508002</v>
       </c>
       <c r="B5" t="n">
-        <v>79218</v>
+        <v>90101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552393</v>
+        <v>552462</v>
       </c>
       <c r="R5" t="n">
-        <v>7037722</v>
+        <v>7037800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B6" t="n">
-        <v>90097</v>
+        <v>79222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R6" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,7 +1240,7 @@
         <v>113508003</v>
       </c>
       <c r="B7" t="n">
-        <v>90025</v>
+        <v>90029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>113511119</v>
       </c>
       <c r="B8" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>81900</v>
+        <v>81906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113508002</v>
+        <v>113511119</v>
       </c>
       <c r="B5" t="n">
-        <v>90101</v>
+        <v>78164</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552462</v>
+        <v>552391</v>
       </c>
       <c r="R5" t="n">
-        <v>7037800</v>
+        <v>7037720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511118</v>
+        <v>113508002</v>
       </c>
       <c r="B6" t="n">
-        <v>79222</v>
+        <v>90107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552393</v>
+        <v>552462</v>
       </c>
       <c r="R6" t="n">
-        <v>7037722</v>
+        <v>7037800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,7 +1240,7 @@
         <v>113508003</v>
       </c>
       <c r="B7" t="n">
-        <v>90029</v>
+        <v>90035</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511119</v>
+        <v>113511118</v>
       </c>
       <c r="B8" t="n">
-        <v>78158</v>
+        <v>79228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552391</v>
+        <v>552393</v>
       </c>
       <c r="R8" t="n">
-        <v>7037720</v>
+        <v>7037722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511116</v>
+        <v>113508003</v>
       </c>
       <c r="B4" t="n">
-        <v>81906</v>
+        <v>90035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552431</v>
+        <v>552365</v>
       </c>
       <c r="R4" t="n">
-        <v>7037803</v>
+        <v>7037714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511119</v>
+        <v>113511116</v>
       </c>
       <c r="B5" t="n">
-        <v>78164</v>
+        <v>81906</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552391</v>
+        <v>552431</v>
       </c>
       <c r="R5" t="n">
-        <v>7037720</v>
+        <v>7037803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B6" t="n">
-        <v>90107</v>
+        <v>79228</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R6" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113508003</v>
+        <v>113508002</v>
       </c>
       <c r="B7" t="n">
-        <v>90035</v>
+        <v>90107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552365</v>
+        <v>552462</v>
       </c>
       <c r="R7" t="n">
-        <v>7037714</v>
+        <v>7037800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511118</v>
+        <v>113511119</v>
       </c>
       <c r="B8" t="n">
-        <v>79228</v>
+        <v>78164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552393</v>
+        <v>552391</v>
       </c>
       <c r="R8" t="n">
-        <v>7037722</v>
+        <v>7037720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113508003</v>
+        <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>90035</v>
+        <v>81913</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552365</v>
+        <v>552431</v>
       </c>
       <c r="R4" t="n">
-        <v>7037714</v>
+        <v>7037803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511116</v>
+        <v>113511118</v>
       </c>
       <c r="B5" t="n">
-        <v>81906</v>
+        <v>79235</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552431</v>
+        <v>552393</v>
       </c>
       <c r="R5" t="n">
-        <v>7037803</v>
+        <v>7037722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511118</v>
+        <v>113508003</v>
       </c>
       <c r="B6" t="n">
-        <v>79228</v>
+        <v>90042</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552393</v>
+        <v>552365</v>
       </c>
       <c r="R6" t="n">
-        <v>7037722</v>
+        <v>7037714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113508002</v>
+        <v>113511119</v>
       </c>
       <c r="B7" t="n">
-        <v>90107</v>
+        <v>78171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552462</v>
+        <v>552391</v>
       </c>
       <c r="R7" t="n">
-        <v>7037800</v>
+        <v>7037720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511119</v>
+        <v>113508002</v>
       </c>
       <c r="B8" t="n">
-        <v>78164</v>
+        <v>90114</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552391</v>
+        <v>552462</v>
       </c>
       <c r="R8" t="n">
-        <v>7037720</v>
+        <v>7037800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511116</v>
+        <v>113508003</v>
       </c>
       <c r="B4" t="n">
-        <v>81913</v>
+        <v>90045</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552431</v>
+        <v>552365</v>
       </c>
       <c r="R4" t="n">
-        <v>7037803</v>
+        <v>7037714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511118</v>
+        <v>113511116</v>
       </c>
       <c r="B5" t="n">
-        <v>79235</v>
+        <v>81916</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552393</v>
+        <v>552431</v>
       </c>
       <c r="R5" t="n">
-        <v>7037722</v>
+        <v>7037803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113508003</v>
+        <v>113511119</v>
       </c>
       <c r="B6" t="n">
-        <v>90042</v>
+        <v>78173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552365</v>
+        <v>552391</v>
       </c>
       <c r="R6" t="n">
-        <v>7037714</v>
+        <v>7037720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511119</v>
+        <v>113508002</v>
       </c>
       <c r="B7" t="n">
-        <v>78171</v>
+        <v>90117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552391</v>
+        <v>552462</v>
       </c>
       <c r="R7" t="n">
-        <v>7037720</v>
+        <v>7037800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B8" t="n">
-        <v>90114</v>
+        <v>79237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R8" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113508003</v>
+        <v>113511118</v>
       </c>
       <c r="B4" t="n">
-        <v>90045</v>
+        <v>79265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552365</v>
+        <v>552393</v>
       </c>
       <c r="R4" t="n">
-        <v>7037714</v>
+        <v>7037722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511116</v>
+        <v>113511119</v>
       </c>
       <c r="B5" t="n">
-        <v>81916</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552431</v>
+        <v>552391</v>
       </c>
       <c r="R5" t="n">
-        <v>7037803</v>
+        <v>7037720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511119</v>
+        <v>113511116</v>
       </c>
       <c r="B6" t="n">
-        <v>78173</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552391</v>
+        <v>552431</v>
       </c>
       <c r="R6" t="n">
-        <v>7037720</v>
+        <v>7037803</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
         <v>113508002</v>
       </c>
       <c r="B7" t="n">
-        <v>90117</v>
+        <v>90148</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511118</v>
+        <v>113508003</v>
       </c>
       <c r="B8" t="n">
-        <v>79237</v>
+        <v>90076</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552393</v>
+        <v>552365</v>
       </c>
       <c r="R8" t="n">
-        <v>7037722</v>
+        <v>7037714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511118</v>
+        <v>113511119</v>
       </c>
       <c r="B4" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552393</v>
+        <v>552391</v>
       </c>
       <c r="R4" t="n">
-        <v>7037722</v>
+        <v>7037720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511119</v>
+        <v>113508003</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>90077</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552391</v>
+        <v>552365</v>
       </c>
       <c r="R5" t="n">
-        <v>7037720</v>
+        <v>7037714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511116</v>
+        <v>113511118</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552431</v>
+        <v>552393</v>
       </c>
       <c r="R6" t="n">
-        <v>7037803</v>
+        <v>7037722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113508002</v>
+        <v>113511116</v>
       </c>
       <c r="B7" t="n">
-        <v>90148</v>
+        <v>81944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552462</v>
+        <v>552431</v>
       </c>
       <c r="R7" t="n">
-        <v>7037800</v>
+        <v>7037803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113508003</v>
+        <v>113508002</v>
       </c>
       <c r="B8" t="n">
-        <v>90076</v>
+        <v>90149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552365</v>
+        <v>552462</v>
       </c>
       <c r="R8" t="n">
-        <v>7037714</v>
+        <v>7037800</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511119</v>
+        <v>113508003</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552391</v>
+        <v>552365</v>
       </c>
       <c r="R4" t="n">
-        <v>7037720</v>
+        <v>7037714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113508003</v>
+        <v>113511116</v>
       </c>
       <c r="B5" t="n">
-        <v>90077</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552365</v>
+        <v>552431</v>
       </c>
       <c r="R5" t="n">
-        <v>7037714</v>
+        <v>7037803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511116</v>
+        <v>113511119</v>
       </c>
       <c r="B7" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552431</v>
+        <v>552391</v>
       </c>
       <c r="R7" t="n">
-        <v>7037803</v>
+        <v>7037720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,7 +1346,7 @@
         <v>113508002</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>90153</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511116</v>
+        <v>113511118</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>79265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552431</v>
+        <v>552393</v>
       </c>
       <c r="R5" t="n">
-        <v>7037803</v>
+        <v>7037722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511118</v>
+        <v>113511116</v>
       </c>
       <c r="B6" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552393</v>
+        <v>552431</v>
       </c>
       <c r="R6" t="n">
-        <v>7037722</v>
+        <v>7037803</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113508003</v>
+        <v>113511119</v>
       </c>
       <c r="B4" t="n">
-        <v>90081</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552365</v>
+        <v>552391</v>
       </c>
       <c r="R4" t="n">
-        <v>7037714</v>
+        <v>7037720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511118</v>
+        <v>113508003</v>
       </c>
       <c r="B5" t="n">
-        <v>79265</v>
+        <v>90081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552393</v>
+        <v>552365</v>
       </c>
       <c r="R5" t="n">
-        <v>7037722</v>
+        <v>7037714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511119</v>
+        <v>113508002</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552391</v>
+        <v>552462</v>
       </c>
       <c r="R7" t="n">
-        <v>7037720</v>
+        <v>7037800</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B8" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R8" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511119</v>
+        <v>113508003</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552391</v>
+        <v>552365</v>
       </c>
       <c r="R4" t="n">
-        <v>7037720</v>
+        <v>7037714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113508003</v>
+        <v>113511116</v>
       </c>
       <c r="B5" t="n">
-        <v>90081</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552365</v>
+        <v>552431</v>
       </c>
       <c r="R5" t="n">
-        <v>7037714</v>
+        <v>7037803</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113511116</v>
+        <v>113508002</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>90153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552431</v>
+        <v>552462</v>
       </c>
       <c r="R6" t="n">
-        <v>7037803</v>
+        <v>7037800</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B7" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R7" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511118</v>
+        <v>113511119</v>
       </c>
       <c r="B8" t="n">
-        <v>79265</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552393</v>
+        <v>552391</v>
       </c>
       <c r="R8" t="n">
-        <v>7037722</v>
+        <v>7037720</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113508003</v>
+        <v>113511116</v>
       </c>
       <c r="B4" t="n">
-        <v>90081</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552365</v>
+        <v>552431</v>
       </c>
       <c r="R4" t="n">
-        <v>7037714</v>
+        <v>7037803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113511116</v>
+        <v>113508003</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>90081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552431</v>
+        <v>552365</v>
       </c>
       <c r="R5" t="n">
-        <v>7037803</v>
+        <v>7037714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113511116</v>
+        <v>113511119</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552431</v>
+        <v>552391</v>
       </c>
       <c r="R4" t="n">
-        <v>7037803</v>
+        <v>7037720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113508003</v>
+        <v>113508002</v>
       </c>
       <c r="B5" t="n">
-        <v>90081</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552365</v>
+        <v>552462</v>
       </c>
       <c r="R5" t="n">
-        <v>7037714</v>
+        <v>7037800</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113508002</v>
+        <v>113511118</v>
       </c>
       <c r="B6" t="n">
-        <v>90153</v>
+        <v>79265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,21 +1147,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552462</v>
+        <v>552393</v>
       </c>
       <c r="R6" t="n">
-        <v>7037800</v>
+        <v>7037722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lindén</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113511118</v>
+        <v>113511116</v>
       </c>
       <c r="B7" t="n">
-        <v>79265</v>
+        <v>81944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552393</v>
+        <v>552431</v>
       </c>
       <c r="R7" t="n">
-        <v>7037722</v>
+        <v>7037803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113511119</v>
+        <v>113508003</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>90081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,21 +1359,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552391</v>
+        <v>552365</v>
       </c>
       <c r="R8" t="n">
-        <v>7037720</v>
+        <v>7037714</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Elin Lindén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 61377-2022 artfynd.xlsx
+++ b/artfynd/A 61377-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
